--- a/data/ground_truth.xlsx
+++ b/data/ground_truth.xlsx
@@ -3008,8 +3008,8 @@
       <c r="A95" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>18</v>
+      <c r="B95" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="4"/>
@@ -3024,8 +3024,8 @@
       <c r="A96" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>18</v>
+      <c r="B96" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="4"/>
